--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486716_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486716_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8452</v>
+        <v>7.5031</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2287</v>
+        <v>8.283799999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3834</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>6.7713</v>
@@ -610,13 +610,13 @@
         <v>2.51</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2922</v>
+        <v>-0.6343</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5797</v>
+        <v>-0.5245</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2875</v>
+        <v>-0.1098</v>
       </c>
       <c r="V2" t="n">
         <v>3.6831</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8729</v>
+        <v>2.1076</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3084</v>
+        <v>2.5432</v>
       </c>
       <c r="F3" t="n">
         <v>-0.4355</v>
@@ -688,10 +688,10 @@
         <v>1.9308</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6894</v>
+        <v>-0.0759</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1027</v>
+        <v>0.3374</v>
       </c>
       <c r="U3" t="n">
         <v>-0.4133</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.818</v>
+        <v>0.9286</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2602</v>
+        <v>2.495</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4422</v>
+        <v>-1.5664</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5122</v>
@@ -766,13 +766,13 @@
         <v>1.5446</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0133</v>
+        <v>1.1239</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5441</v>
+        <v>0.7789</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4692</v>
+        <v>0.345</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2277</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. REYES ZUR</t>
+          <t>B. VIDARTE CANO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6256</v>
+        <v>-0.6599</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0614</v>
+        <v>1.8342</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-2.4941</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1993</v>
+        <v>-1.3688</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0207</v>
+        <v>1.1314</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1786</v>
+        <v>-2.5002</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0614</v>
+        <v>1.5433</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0207</v>
+        <v>2.9945</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0407</v>
+        <v>-1.4512</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1379</v>
+        <v>-2.9121</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-1.8631</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1379</v>
+        <v>-1.049</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1931</v>
+        <v>2.51</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1931</v>
+        <v>2.51</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2097</v>
+        <v>-1.1446</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.5659</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2097</v>
+        <v>-0.5787</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2277</v>
+        <v>-0.6565</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.8568</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2277</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. VIDARTE CANO</t>
+          <t>P. REYES ZUR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5398</v>
+        <v>-0.725</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1033</v>
+        <v>0.0614</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.6431</v>
+        <v>-0.7863</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3688</v>
+        <v>0.1993</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1314</v>
+        <v>0.0207</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.5002</v>
+        <v>0.1786</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5433</v>
+        <v>0.0614</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9945</v>
+        <v>0.0207</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4512</v>
+        <v>0.0407</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.9121</v>
+        <v>0.1379</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8631</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.049</v>
+        <v>0.1379</v>
       </c>
       <c r="P6" t="n">
-        <v>2.51</v>
+        <v>0.1931</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.51</v>
+        <v>0.1931</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.0245</v>
+        <v>0.1104</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2968</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7277</v>
+        <v>0.1104</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6565</v>
+        <v>-1.2277</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8568</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.5133</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7234</v>
+        <v>-0.871</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8465</v>
+        <v>-0.2673</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8768</v>
+        <v>-0.6037</v>
       </c>
       <c r="G7" t="n">
         <v>0.7316</v>
@@ -1000,13 +1000,13 @@
         <v>1.7377</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.949</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5795</v>
+        <v>-0.0002</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3695</v>
+        <v>-0.0963</v>
       </c>
       <c r="V7" t="n">
         <v>-1.3129</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
+          <t>P. GRANJA I BERNAD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3194</v>
+        <v>-2.006</v>
       </c>
       <c r="E8" t="n">
-        <v>1.34</v>
+        <v>-0.4369</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.6594</v>
+        <v>-1.5691</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8334</v>
+        <v>-2.6993</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8552</v>
+        <v>-0.6828</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0218</v>
+        <v>-2.0165</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8094</v>
+        <v>-0.5401</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2682</v>
+        <v>-0.5446</v>
       </c>
       <c r="L8" t="n">
-        <v>2.0776</v>
+        <v>0.0046</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.6428</v>
+        <v>-2.1593</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.587</v>
+        <v>-0.1382</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0558</v>
+        <v>-2.0211</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9308</v>
+        <v>1.3515</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9308</v>
+        <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.004</v>
+        <v>0.2413</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4693</v>
+        <v>0.1032</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5347</v>
+        <v>0.1381</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.4128</v>
+        <v>-0.8995</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4128</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. BUENO KNUTSEN</t>
+          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8304</v>
+        <v>-2.5497</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0422</v>
+        <v>1.0849</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7882</v>
+        <v>-3.6346</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1534</v>
+        <v>-0.8334</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6899</v>
+        <v>-1.8552</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4634</v>
+        <v>1.0218</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4404</v>
+        <v>1.8094</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8277</v>
+        <v>-0.2682</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6127</v>
+        <v>2.0776</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.5937</v>
+        <v>-2.6428</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5176</v>
+        <v>-1.587</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0761</v>
+        <v>-1.0558</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1585</v>
+        <v>1.9308</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7723</v>
+        <v>1.9308</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-1.2343</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5518</v>
+        <v>-0.7244</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0332</v>
+        <v>-0.5098</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.4128</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.4128</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. GRANJA I BERNAD</t>
+          <t>E. BUENO KNUTSEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8818</v>
+        <v>-2.7808</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0643</v>
+        <v>-1.0422</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8174</v>
+        <v>-1.7385</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6993</v>
+        <v>-1.1534</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6828</v>
+        <v>-0.6899</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.0165</v>
+        <v>-0.4634</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5401</v>
+        <v>1.4404</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5446</v>
+        <v>0.8277</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0046</v>
+        <v>0.6127</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1593</v>
+        <v>-2.5937</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1382</v>
+        <v>-1.5176</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.0211</v>
+        <v>-1.0761</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3515</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3515</v>
+        <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6345</v>
+        <v>-0.4689</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5243</v>
+        <v>-0.5518</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1102</v>
+        <v>0.0829</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.8995</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.1056</v>
+        <v>-5.6092</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.263</v>
+        <v>-2.6425</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8426</v>
+        <v>-2.9668</v>
       </c>
       <c r="G11" t="n">
         <v>-3.3362</v>
@@ -1312,13 +1312,13 @@
         <v>1.9308</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2135</v>
+        <v>-0.7171</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9933</v>
+        <v>-0.3727</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2202</v>
+        <v>-0.3444</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5559</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.489900000000001</v>
+        <v>-4.6623</v>
       </c>
       <c r="E12" t="n">
-        <v>11.086</v>
+        <v>11.9136</v>
       </c>
       <c r="F12" t="n">
-        <v>-16.5756</v>
+        <v>-16.5757</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6201</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4152</v>
+        <v>2.415200000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.0353</v>
+        <v>-4.035299999999999</v>
       </c>
       <c r="J12" t="n">
         <v>19.3555</v>
@@ -1390,13 +1390,13 @@
         <v>16.4116</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.7239</v>
+        <v>-2.8961</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.3479</v>
+        <v>-1.52</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.376</v>
+        <v>-1.3759</v>
       </c>
       <c r="V12" t="n">
         <v>-5.938099999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.9032</v>
+        <v>6.2687</v>
       </c>
       <c r="E13" t="n">
-        <v>8.3725</v>
+        <v>8.476000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4693</v>
+        <v>-2.2073</v>
       </c>
       <c r="G13" t="n">
         <v>2.0536</v>
@@ -1468,13 +1468,13 @@
         <v>1.7377</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3861</v>
+        <v>-0.0206</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2211</v>
+        <v>-0.1177</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.165</v>
+        <v>0.097</v>
       </c>
       <c r="V13" t="n">
         <v>2.498</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.1022</v>
+        <v>5.0622</v>
       </c>
       <c r="E14" t="n">
-        <v>6.7974</v>
+        <v>6.694</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6953</v>
+        <v>-1.6319</v>
       </c>
       <c r="G14" t="n">
         <v>0.4109</v>
@@ -1546,13 +1546,13 @@
         <v>1.7377</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1088</v>
+        <v>1.0688</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6339</v>
+        <v>0.5305</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4749</v>
+        <v>0.5383</v>
       </c>
       <c r="V14" t="n">
         <v>3.9687</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.205</v>
+        <v>1.0767</v>
       </c>
       <c r="E15" t="n">
-        <v>1.683</v>
+        <v>1.0625</v>
       </c>
       <c r="F15" t="n">
-        <v>0.522</v>
+        <v>0.0142</v>
       </c>
       <c r="G15" t="n">
         <v>2.0451</v>
@@ -1624,13 +1624,13 @@
         <v>0.5792</v>
       </c>
       <c r="S15" t="n">
-        <v>2.604</v>
+        <v>1.4757</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3511</v>
+        <v>0.7305</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2529</v>
+        <v>0.7452</v>
       </c>
       <c r="V15" t="n">
         <v>-0.8995</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3144</v>
+        <v>0.8689</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6893</v>
+        <v>3.8961</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.3749</v>
+        <v>-3.0272</v>
       </c>
       <c r="G16" t="n">
         <v>3.833</v>
@@ -1702,13 +1702,13 @@
         <v>0.5792</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.982</v>
+        <v>-0.4275</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7174</v>
+        <v>-0.5105</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2646</v>
+        <v>0.083</v>
       </c>
       <c r="V16" t="n">
         <v>-1.1851</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0631</v>
+        <v>0.6313</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3058</v>
+        <v>-0.099</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3689</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>0.3831</v>
@@ -1780,13 +1780,13 @@
         <v>0.7723</v>
       </c>
       <c r="S17" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.6344</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0825</v>
+        <v>0.2893</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0163</v>
+        <v>0.3451</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H. APARICIO RODRÍGUEZ</t>
+          <t>M. SOLA IDRISU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8109</v>
+        <v>-0.4785</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9654</v>
+        <v>0.6746</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1545</v>
+        <v>-1.1531</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1379</v>
+        <v>-2.6949</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1379</v>
+        <v>-2.0823</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-0.6126</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.5686</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.0125</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1379</v>
+        <v>-3.2635</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1379</v>
+        <v>-2.0698</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-1.1937</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9654</v>
+        <v>1.7377</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.7377</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0166</v>
+        <v>0.1931</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.1797</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0166</v>
+        <v>0.3728</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. TUSAMBA SOLIS</t>
+          <t>G. PEREZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1014</v>
+        <v>-0.4865</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9799</v>
+        <v>-0.3865</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1215</v>
+        <v>-0.1001</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0974</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2759</v>
+        <v>-0.5866</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1786</v>
+        <v>-0.2283</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0407</v>
+        <v>-0.421</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-0.586</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0407</v>
+        <v>0.1651</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1381</v>
+        <v>-0.394</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2759</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1379</v>
+        <v>-0.3934</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9654</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9654</v>
+        <v>-1.1585</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.7723</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0386</v>
+        <v>-0.2275</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0552</v>
+        <v>-0.0347</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0166</v>
+        <v>-0.1928</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.9421</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. PEREZ HERNANDEZ</t>
+          <t>H. APARICIO RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2905</v>
+        <v>-0.7861</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9036</v>
+        <v>-0.9654</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.387</v>
+        <v>0.1793</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8149999999999999</v>
+        <v>0.1379</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5866</v>
+        <v>0.1379</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2283</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.421</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1651</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.394</v>
+        <v>0.1379</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.1379</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3934</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3862</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1585</v>
+        <v>-0.9654</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7723</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0315</v>
+        <v>0.0414</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5518</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4797</v>
+        <v>0.0414</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9421</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. SANCHEZ PEREZ</t>
+          <t>J. TUSAMBA SOLIS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3367</v>
+        <v>-1.0765</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7458</v>
+        <v>-0.9799</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0824</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.8546</v>
+        <v>-0.0974</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3445</v>
+        <v>-0.2759</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5101</v>
+        <v>0.1786</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6912</v>
+        <v>0.0407</v>
       </c>
       <c r="K21" t="n">
-        <v>0.725</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0338</v>
+        <v>0.0407</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.5458</v>
+        <v>-0.1381</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0695</v>
+        <v>-0.2759</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4763</v>
+        <v>0.1379</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7723</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1239</v>
+        <v>-0.9654</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3515</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.5759</v>
+        <v>-0.0138</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1784</v>
+        <v>-0.0552</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3974</v>
+        <v>0.0414</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. SOLA IDRISU</t>
+          <t>D. SANCHEZ PEREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3722</v>
+        <v>-2.375</v>
       </c>
       <c r="E22" t="n">
-        <v>0.054</v>
+        <v>-0.3919</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4262</v>
+        <v>-1.9831</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6949</v>
+        <v>-2.8546</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0823</v>
+        <v>-1.3445</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6126</v>
+        <v>-1.5101</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5686</v>
+        <v>0.6912</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0125</v>
+        <v>0.725</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5810999999999999</v>
+        <v>-0.0338</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.2635</v>
+        <v>-3.5458</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.0698</v>
+        <v>-2.0695</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1937</v>
+        <v>-1.4763</v>
       </c>
       <c r="P22" t="n">
-        <v>1.7377</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.1239</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7377</v>
+        <v>1.3515</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7006</v>
+        <v>1.5376</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8002</v>
+        <v>1.0408</v>
       </c>
       <c r="U22" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.4968</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2856</v>
+        <v>-0.2856</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1863</v>
+        <v>-2.5257</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6116</v>
+        <v>-1.4048</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5746</v>
+        <v>-1.1209</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7814</v>
@@ -2248,13 +2248,13 @@
         <v>1.3515</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4913</v>
+        <v>0.1518</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5243</v>
+        <v>-0.3174</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0156</v>
+        <v>0.4693</v>
       </c>
       <c r="V23" t="n">
         <v>0.6138</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.489899999999999</v>
+        <v>6.179500000000001</v>
       </c>
       <c r="E24" t="n">
         <v>16.5757</v>
       </c>
       <c r="F24" t="n">
-        <v>-11.0858</v>
+        <v>-10.3965</v>
       </c>
       <c r="G24" t="n">
         <v>1.620299999999999</v>
@@ -2326,13 +2326,13 @@
         <v>10.6191</v>
       </c>
       <c r="S24" t="n">
-        <v>3.724</v>
+        <v>4.4134</v>
       </c>
       <c r="T24" t="n">
         <v>1.3759</v>
       </c>
       <c r="U24" t="n">
-        <v>2.348</v>
+        <v>3.0375</v>
       </c>
       <c r="V24" t="n">
         <v>5.938000000000001</v>
